--- a/Team-Data/2007-08/12-29-2007-08.xlsx
+++ b/Team-Data/2007-08/12-29-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,91 +728,91 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.536</v>
+        <v>0.556</v>
       </c>
       <c r="H2" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="J2" t="n">
-        <v>77</v>
+        <v>77.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M2" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.321</v>
+        <v>0.324</v>
       </c>
       <c r="O2" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="P2" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R2" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S2" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T2" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U2" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="V2" t="n">
         <v>15.6</v>
       </c>
       <c r="W2" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
         <v>5.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -781,40 +848,40 @@
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
         <v>20</v>
       </c>
       <c r="AU2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ2" t="n">
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.893</v>
+        <v>0.889</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
@@ -861,22 +928,22 @@
         <v>35.5</v>
       </c>
       <c r="J3" t="n">
-        <v>75.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L3" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M3" t="n">
         <v>19.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.397</v>
+        <v>0.394</v>
       </c>
       <c r="O3" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="P3" t="n">
         <v>27.9</v>
@@ -885,10 +952,10 @@
         <v>0.772</v>
       </c>
       <c r="R3" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
         <v>41.7</v>
@@ -897,16 +964,16 @@
         <v>22.6</v>
       </c>
       <c r="V3" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
         <v>21</v>
@@ -915,13 +982,13 @@
         <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>8</v>
       </c>
       <c r="AI3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,7 +1012,7 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM3" t="n">
         <v>10</v>
@@ -960,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -969,31 +1036,31 @@
         <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>0.357</v>
+        <v>0.37</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
@@ -1043,16 +1110,16 @@
         <v>34.4</v>
       </c>
       <c r="J4" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L4" t="n">
         <v>6.3</v>
       </c>
       <c r="M4" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N4" t="n">
         <v>0.367</v>
@@ -1061,22 +1128,22 @@
         <v>18</v>
       </c>
       <c r="P4" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="S4" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="T4" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V4" t="n">
         <v>16</v>
@@ -1085,55 +1152,55 @@
         <v>7.8</v>
       </c>
       <c r="X4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y4" t="n">
         <v>5.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
       </c>
       <c r="AF4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG4" t="n">
         <v>23</v>
       </c>
-      <c r="AG4" t="n">
-        <v>24</v>
-      </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
         <v>20</v>
@@ -1145,7 +1212,7 @@
         <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
         <v>30</v>
@@ -1160,7 +1227,7 @@
         <v>23</v>
       </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
         <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>23</v>
@@ -1303,7 +1370,7 @@
         <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1318,7 +1385,7 @@
         <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
         <v>25</v>
@@ -1330,10 +1397,10 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
         <v>14</v>
@@ -1351,7 +1418,7 @@
         <v>29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>19</v>
@@ -1360,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -1389,94 +1456,94 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.452</v>
+        <v>0.467</v>
       </c>
       <c r="H6" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J6" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.432</v>
+        <v>0.434</v>
       </c>
       <c r="L6" t="n">
         <v>6.5</v>
       </c>
       <c r="M6" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="O6" t="n">
         <v>18.6</v>
       </c>
-      <c r="N6" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="O6" t="n">
-        <v>18.2</v>
-      </c>
       <c r="P6" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.717</v>
+        <v>0.718</v>
       </c>
       <c r="R6" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U6" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="V6" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X6" t="n">
         <v>4.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB6" t="n">
-        <v>95.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="AD6" t="n">
         <v>3</v>
       </c>
       <c r="AE6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF6" t="n">
         <v>18</v>
       </c>
-      <c r="AF6" t="n">
-        <v>20</v>
-      </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
@@ -1488,7 +1555,7 @@
         <v>13</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>13</v>
@@ -1497,25 +1564,25 @@
         <v>13</v>
       </c>
       <c r="AN6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>26</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>15</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
         <v>27</v>
@@ -1524,22 +1591,22 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
         <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
         <v>24</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC6" t="n">
         <v>20</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -1571,88 +1638,88 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.645</v>
+        <v>0.633</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>77.8</v>
+        <v>78</v>
       </c>
       <c r="K7" t="n">
         <v>0.466</v>
       </c>
       <c r="L7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M7" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.349</v>
+        <v>0.344</v>
       </c>
       <c r="O7" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="P7" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.828</v>
+        <v>0.831</v>
       </c>
       <c r="R7" t="n">
         <v>10.3</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T7" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U7" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="X7" t="n">
         <v>5.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
         <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
         <v>7</v>
@@ -1667,58 +1734,58 @@
         <v>17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
         <v>5</v>
       </c>
       <c r="AL7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>19</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
         <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1852,13 +1919,13 @@
         <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL8" t="n">
         <v>14</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN8" t="n">
         <v>23</v>
@@ -1873,7 +1940,7 @@
         <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
         <v>4</v>
@@ -1885,7 +1952,7 @@
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.767</v>
+        <v>0.759</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J9" t="n">
-        <v>79.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L9" t="n">
         <v>5.6</v>
@@ -1965,43 +2032,43 @@
         <v>15.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O9" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.762</v>
+        <v>0.759</v>
       </c>
       <c r="R9" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="S9" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T9" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U9" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="W9" t="n">
         <v>7.1</v>
       </c>
       <c r="X9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y9" t="n">
         <v>3.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" t="n">
         <v>20.7</v>
@@ -2010,10 +2077,10 @@
         <v>99.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,7 +2095,7 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
@@ -2043,22 +2110,22 @@
         <v>23</v>
       </c>
       <c r="AN9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>11</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
         <v>24</v>
@@ -2073,7 +2140,7 @@
         <v>19</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>10</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2225,28 +2292,28 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR10" t="n">
         <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
         <v>7</v>
@@ -2258,13 +2325,13 @@
         <v>22</v>
       </c>
       <c r="AY10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ10" t="n">
         <v>25</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -2299,55 +2366,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.483</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="J11" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.436</v>
+        <v>0.438</v>
       </c>
       <c r="L11" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.339</v>
+        <v>0.334</v>
       </c>
       <c r="O11" t="n">
         <v>16.2</v>
       </c>
       <c r="P11" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.724</v>
+        <v>0.719</v>
       </c>
       <c r="R11" t="n">
         <v>12.7</v>
       </c>
       <c r="S11" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="T11" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
         <v>21</v>
@@ -2365,34 +2432,34 @@
         <v>4.8</v>
       </c>
       <c r="Z11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AA11" t="n">
         <v>20.5</v>
       </c>
-      <c r="AA11" t="n">
-        <v>20.3</v>
-      </c>
       <c r="AB11" t="n">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="n">
         <v>11</v>
@@ -2416,13 +2483,13 @@
         <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR11" t="n">
         <v>4</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
         <v>3</v>
@@ -2443,7 +2510,7 @@
         <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
         <v>23</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
         <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.484</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="J12" t="n">
-        <v>86.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="K12" t="n">
         <v>0.445</v>
@@ -2508,10 +2575,10 @@
         <v>8.1</v>
       </c>
       <c r="M12" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="O12" t="n">
         <v>18.6</v>
@@ -2520,10 +2587,10 @@
         <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
         <v>32.5</v>
@@ -2532,16 +2599,16 @@
         <v>44.3</v>
       </c>
       <c r="U12" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V12" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W12" t="n">
         <v>7.5</v>
       </c>
       <c r="X12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y12" t="n">
         <v>5.7</v>
@@ -2553,10 +2620,10 @@
         <v>22.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.6</v>
+        <v>104</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="AD12" t="n">
         <v>3</v>
@@ -2565,10 +2632,10 @@
         <v>14</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
@@ -2580,19 +2647,19 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
         <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP12" t="n">
         <v>19</v>
@@ -2610,13 +2677,13 @@
         <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2771,13 +2838,13 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
@@ -2786,16 +2853,16 @@
         <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>12</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
         <v>22</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2953,19 +3020,19 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>2</v>
@@ -2974,10 +3041,10 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -3105,31 +3172,31 @@
         <v>-4.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
         <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>18</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
@@ -3138,7 +3205,7 @@
         <v>5</v>
       </c>
       <c r="AO15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
         <v>17</v>
@@ -3150,22 +3217,22 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.258</v>
+        <v>0.267</v>
       </c>
       <c r="H16" t="n">
         <v>48.5</v>
       </c>
       <c r="I16" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="J16" t="n">
-        <v>77</v>
+        <v>77.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M16" t="n">
         <v>13.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.332</v>
+        <v>0.328</v>
       </c>
       <c r="O16" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="P16" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.702</v>
+        <v>0.704</v>
       </c>
       <c r="R16" t="n">
         <v>9.6</v>
@@ -3260,37 +3327,37 @@
         <v>39.5</v>
       </c>
       <c r="U16" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="V16" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
         <v>7.6</v>
       </c>
       <c r="X16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>94</v>
+        <v>94.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>-5.3</v>
+        <v>-4.7</v>
       </c>
       <c r="AD16" t="n">
         <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF16" t="n">
         <v>29</v>
@@ -3302,13 +3369,13 @@
         <v>6</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3317,16 +3384,16 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
         <v>28</v>
@@ -3338,31 +3405,31 @@
         <v>29</v>
       </c>
       <c r="AU16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
         <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ16" t="n">
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -3391,64 +3458,64 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" t="n">
         <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.379</v>
+        <v>0.393</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J17" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K17" t="n">
         <v>0.452</v>
       </c>
       <c r="L17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="O17" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.741</v>
+        <v>0.744</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T17" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V17" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X17" t="n">
         <v>4.8</v>
@@ -3460,31 +3527,31 @@
         <v>21.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-5</v>
+        <v>-5.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ17" t="n">
         <v>14</v>
@@ -3502,7 +3569,7 @@
         <v>22</v>
       </c>
       <c r="AO17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
         <v>23</v>
@@ -3511,7 +3578,7 @@
         <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
         <v>27</v>
@@ -3523,7 +3590,7 @@
         <v>12</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
@@ -3532,7 +3599,7 @@
         <v>17</v>
       </c>
       <c r="AY17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ17" t="n">
         <v>19</v>
@@ -3541,10 +3608,10 @@
         <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
-        <v>0.138</v>
+        <v>0.143</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3591,67 +3658,67 @@
         <v>36.6</v>
       </c>
       <c r="J18" t="n">
-        <v>83.7</v>
+        <v>83.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="L18" t="n">
         <v>5.9</v>
       </c>
       <c r="M18" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O18" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="P18" t="n">
         <v>20.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.72</v>
+        <v>0.726</v>
       </c>
       <c r="R18" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S18" t="n">
         <v>29.4</v>
       </c>
       <c r="T18" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
-        <v>16.1</v>
+        <v>16.4</v>
       </c>
       <c r="W18" t="n">
         <v>7.4</v>
       </c>
       <c r="X18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3675,13 +3742,13 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM18" t="n">
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,31 +3757,31 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -3755,64 +3822,64 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.467</v>
+        <v>0.448</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
       </c>
       <c r="I19" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="J19" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.434</v>
+        <v>0.431</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.317</v>
+        <v>0.32</v>
       </c>
       <c r="O19" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="P19" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.737</v>
+        <v>0.742</v>
       </c>
       <c r="R19" t="n">
         <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T19" t="n">
         <v>41.4</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="V19" t="n">
         <v>16.2</v>
       </c>
       <c r="W19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="X19" t="n">
         <v>4.9</v>
@@ -3821,28 +3888,28 @@
         <v>3.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA19" t="n">
         <v>23.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5</v>
+        <v>-5.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF19" t="n">
         <v>18</v>
       </c>
-      <c r="AF19" t="n">
-        <v>16</v>
-      </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>4</v>
@@ -3854,49 +3921,49 @@
         <v>29</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>23</v>
       </c>
       <c r="AM19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP19" t="n">
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
         <v>22</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
@@ -3908,7 +3975,7 @@
         <v>29</v>
       </c>
       <c r="BC19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -3937,88 +4004,88 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>0.667</v>
+        <v>0.655</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="J20" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L20" t="n">
         <v>7.4</v>
       </c>
       <c r="M20" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="O20" t="n">
         <v>15.6</v>
       </c>
       <c r="P20" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.789</v>
+        <v>0.79</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
         <v>31.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U20" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V20" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X20" t="n">
         <v>4.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z20" t="n">
         <v>19.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4030,13 +4097,13 @@
         <v>4</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
@@ -4045,7 +4112,7 @@
         <v>7</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>28</v>
@@ -4066,10 +4133,10 @@
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
@@ -4090,7 +4157,7 @@
         <v>17</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-7.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
@@ -4224,19 +4291,19 @@
         <v>21</v>
       </c>
       <c r="AM21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR21" t="n">
         <v>2</v>
@@ -4251,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
         <v>22</v>
@@ -4263,13 +4330,13 @@
         <v>28</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
         <v>11</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
         <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>0.656</v>
+        <v>0.645</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
@@ -4322,52 +4389,52 @@
         <v>79.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="M22" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="N22" t="n">
         <v>0.353</v>
       </c>
       <c r="O22" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="P22" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="Q22" t="n">
         <v>0.713</v>
       </c>
       <c r="R22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="T22" t="n">
         <v>43.7</v>
       </c>
       <c r="U22" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="V22" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W22" t="n">
         <v>6.2</v>
       </c>
       <c r="X22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y22" t="n">
         <v>4.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA22" t="n">
         <v>24.2</v>
@@ -4376,31 +4443,31 @@
         <v>103.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
         <v>7</v>
       </c>
       <c r="AG22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH22" t="n">
         <v>7</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
         <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL22" t="n">
         <v>2</v>
@@ -4409,10 +4476,10 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
@@ -4433,7 +4500,7 @@
         <v>15</v>
       </c>
       <c r="AV22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW22" t="n">
         <v>26</v>
@@ -4442,7 +4509,7 @@
         <v>20</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
         <v>13</v>
@@ -4451,7 +4518,7 @@
         <v>2</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC22" t="n">
         <v>9</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -4561,19 +4628,19 @@
         <v>-0.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI23" t="n">
         <v>20</v>
@@ -4582,7 +4649,7 @@
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>28</v>
@@ -4591,7 +4658,7 @@
         <v>28</v>
       </c>
       <c r="AN23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO23" t="n">
         <v>21</v>
@@ -4612,22 +4679,22 @@
         <v>14</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
         <v>24</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>22</v>
@@ -4636,7 +4703,7 @@
         <v>26</v>
       </c>
       <c r="BC23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4770,13 +4837,13 @@
         <v>3</v>
       </c>
       <c r="AM24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN24" t="n">
         <v>6</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
         <v>26</v>
@@ -4806,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="AY24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4940,16 +5007,16 @@
         <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
         <v>20</v>
@@ -4967,10 +5034,10 @@
         <v>18</v>
       </c>
       <c r="AR25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
@@ -4997,10 +5064,10 @@
         <v>17</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -5107,19 +5174,19 @@
         <v>-3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>21</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
         <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>24</v>
@@ -5131,7 +5198,7 @@
         <v>17</v>
       </c>
       <c r="AL26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM26" t="n">
         <v>21</v>
@@ -5143,10 +5210,10 @@
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR26" t="n">
         <v>24</v>
@@ -5179,7 +5246,7 @@
         <v>4</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>6.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
@@ -5304,7 +5371,7 @@
         <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ27" t="n">
         <v>20</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
         <v>25</v>
@@ -5337,10 +5404,10 @@
         <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
@@ -5358,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -5393,103 +5460,103 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="n">
         <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3</v>
+        <v>0.276</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J28" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.442</v>
+        <v>0.439</v>
       </c>
       <c r="L28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M28" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.358</v>
+        <v>0.354</v>
       </c>
       <c r="O28" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P28" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.774</v>
       </c>
       <c r="R28" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S28" t="n">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="T28" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="U28" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="V28" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="W28" t="n">
         <v>7</v>
       </c>
       <c r="X28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>98.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>-6.1</v>
+        <v>-7</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF28" t="n">
         <v>27</v>
       </c>
       <c r="AG28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AI28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK28" t="n">
         <v>23</v>
@@ -5501,7 +5568,7 @@
         <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO28" t="n">
         <v>16</v>
@@ -5510,7 +5577,7 @@
         <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
         <v>15</v>
@@ -5522,7 +5589,7 @@
         <v>2</v>
       </c>
       <c r="AU28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5531,7 +5598,7 @@
         <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
         <v>20</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -5575,82 +5642,82 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
-        <v>0.516</v>
+        <v>0.533</v>
       </c>
       <c r="H29" t="n">
         <v>48.2</v>
       </c>
       <c r="I29" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J29" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="K29" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="L29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="M29" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.417</v>
+        <v>0.421</v>
       </c>
       <c r="O29" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="P29" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="S29" t="n">
         <v>30.9</v>
       </c>
       <c r="T29" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="U29" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="V29" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W29" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
         <v>3</v>
@@ -5659,10 +5726,10 @@
         <v>12</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
         <v>21</v>
@@ -5671,13 +5738,13 @@
         <v>10</v>
       </c>
       <c r="AJ29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5701,34 +5768,34 @@
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AU29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA29" t="n">
         <v>30</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>0.516</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,64 +5842,64 @@
         <v>39.5</v>
       </c>
       <c r="J30" t="n">
-        <v>81</v>
+        <v>81.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.488</v>
+        <v>0.486</v>
       </c>
       <c r="L30" t="n">
         <v>3.7</v>
       </c>
       <c r="M30" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O30" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="P30" t="n">
-        <v>29.3</v>
+        <v>29.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R30" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="S30" t="n">
-        <v>28.8</v>
+        <v>29</v>
       </c>
       <c r="T30" t="n">
-        <v>41.3</v>
+        <v>41.6</v>
       </c>
       <c r="U30" t="n">
         <v>25.5</v>
       </c>
       <c r="V30" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W30" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>104.6</v>
+        <v>104.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5841,10 +5908,10 @@
         <v>12</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5871,31 +5938,31 @@
         <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ30" t="n">
         <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AS30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AY30" t="n">
         <v>30</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F31" t="n">
         <v>14</v>
       </c>
       <c r="G31" t="n">
-        <v>0.517</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.451</v>
+        <v>0.448</v>
       </c>
       <c r="L31" t="n">
         <v>6.6</v>
@@ -5969,76 +6036,76 @@
         <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O31" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P31" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="R31" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="S31" t="n">
         <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="U31" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="V31" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W31" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
         <v>5.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z31" t="n">
         <v>19.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.2</v>
+        <v>100.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF31" t="n">
         <v>13</v>
       </c>
       <c r="AG31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL31" t="n">
         <v>12</v>
@@ -6047,19 +6114,19 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP31" t="n">
         <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
         <v>13</v>
@@ -6068,31 +6135,31 @@
         <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV31" t="n">
         <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-29-2007-08</t>
+          <t>2007-12-29</t>
         </is>
       </c>
     </row>
